--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 80分钟</t>
+          <t>SHMAAS末次终点ETA推算：07:00采样，终点ETA 61分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -753,26 +753,22 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 61分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -780,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -804,37 +800,33 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -842,24 +834,24 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -872,7 +864,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -884,22 +876,22 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±15分钟</t>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -923,12 +915,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -953,7 +945,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +953,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -971,7 +963,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -991,7 +983,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1003,22 +995,22 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±11分钟</t>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1032,47 +1024,1467 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>06:50</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>114分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站张杨北路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>3/4</t>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数99分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -753,19 +753,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>116分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 61分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +800,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +820,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -859,29 +863,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -915,12 +919,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -930,22 +934,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -978,29 +982,29 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1034,12 +1038,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1049,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1102,19 +1106,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1129,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1178,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1220,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1248,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1272,12 +1276,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1287,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1340,26 +1344,22 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 17分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1459,24 +1459,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±14分钟</t>
+          <t>07:30采样：该车到重点站金高路万安街 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±11分钟</t>
+          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1697,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1816,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站张杨北路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2054,24 +2054,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+          <t>08:10采样：该车到重点站五莲路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2173,24 +2173,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±11分钟</t>
+          <t>08:10采样：该车到重点站航津路地铁站 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2292,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数99分钟估算，约±6分钟</t>
+          <t>08:10采样：该车到重点站金杨路金桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2381,24 +2381,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2411,30 +2411,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>08:10采样：该车到重点站航津路地铁站 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2448,43 +2452,876 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站同港路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>08:11</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数102分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>113分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -987,24 +987,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1106,19 +1106,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
+          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数17分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1356,10 +1356,14 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 17分钟</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1391,12 +1395,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1459,24 +1463,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:30采样：该车到重点站金高路万安街 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站云山路灵山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,7 +1539,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1697,26 +1701,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1816,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±8分钟</t>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2054,24 +2054,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站五莲路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±10分钟</t>
+          <t>08:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2173,24 +2173,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站航津路地铁站 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
+          <t>08:20采样：该车到重点站金高路东靖路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2292,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路金桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±11分钟</t>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2530,19 +2530,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站同港路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站花山路大同路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2649,19 +2649,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+          <t>08:20采样：该车到重点站花山路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2768,26 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2815,17 +2819,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2835,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,12 +2963,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,24 +3214,24 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3240,34 +3244,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3320,246 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>113分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>11/18</t>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,11 +449,11 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -632,29 +632,29 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程54%处后消失；随后反向物理轨迹由seq26推进至seq37，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:00采样，终点ETA 61分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -673,10 +673,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>巨峰路五莲路</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -694,7 +706,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -825,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -944,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1101,24 +1113,24 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数17分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1133,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1157,12 +1169,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1182,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1301,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1420,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1463,26 +1475,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站云山路灵山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1490,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1519,7 +1527,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1529,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1577,24 +1585,24 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1609,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,12 +1641,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1648,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1704,31 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1724,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1748,12 +1760,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1768,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1823,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1867,12 +1879,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1882,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2049,24 +2061,24 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2081,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2105,12 +2117,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2120,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2173,26 +2185,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金高路东靖路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2200,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2229,7 +2237,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2249,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2287,29 +2295,29 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站五莲路凌河路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2319,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,12 +2351,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2358,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2406,29 +2414,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站航津路地铁站 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2438,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,12 +2470,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2477,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2530,26 +2538,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站花山路大同路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,12 +2585,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2606,12 +2610,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2649,19 +2653,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站花山路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+          <t>09:20采样：该车到重点站丁香路金松路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数5分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2768,26 +2772,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站五莲路凌河路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 29分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2887,24 +2887,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±10分钟</t>
+          <t>09:20采样：该车到重点站金高路俱进路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3006,24 +3006,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数102分钟估算，约±15分钟</t>
+          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3125,24 +3125,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>09:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3214,24 +3214,24 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3244,34 +3244,34 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±12分钟</t>
+          <t>09:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3333,24 +3333,24 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3363,19 +3363,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+          <t>09:00采样：该车到重点站张杨北路金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3452,24 +3452,24 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3482,30 +3482,34 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3519,7 +3523,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3529,37 +3533,985 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站杨高北路夏碧路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>107.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2533,27 +2533,31 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,12 +2589,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2610,7 +2614,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2653,26 +2657,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站丁香路金松路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数5分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:30采样，终点ETA 29分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2767,27 +2767,31 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 29分钟</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,12 +2823,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2839,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2882,29 +2886,29 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金高路俱进路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2938,12 +2942,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2953,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3001,29 +3005,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,12 +3061,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3072,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3120,29 +3124,29 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3176,12 +3180,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3201,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3239,24 +3243,24 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,12 +3299,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3310,22 +3314,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3363,26 +3367,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:00采样：该车到重点站张杨北路金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:10采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3482,24 +3482,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>同车下一次反向发车10:45，减去该车自身同类时段历史终点停站中位数21分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3548,22 +3548,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3596,24 +3596,24 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站杨高北路夏碧路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3667,17 +3667,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3720,26 +3720,22 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3747,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,7 +3772,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3796,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3839,26 +3835,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3866,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3895,7 +3887,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3915,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3958,26 +3950,22 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -3985,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,12 +3997,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4024,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4077,24 +4065,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±9分钟</t>
+          <t>10:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4104,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,7 +4121,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4153,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4196,24 +4184,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+          <t>10:20采样：该车到重点站五莲路归昌路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4223,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,12 +4235,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4272,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4315,19 +4303,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4342,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4371,7 +4359,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4391,7 +4379,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4414,7 +4402,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4434,22 +4422,26 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>10:20采样：该车到重点站杨高北路航津路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4457,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4471,7 +4463,7 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4481,35 +4473,864 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站云山路灵山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站云山路灵山路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站金高路东靖路 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr">
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
         </is>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3715,27 +3715,31 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 13分钟</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,12 +3771,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3792,7 +3796,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3830,27 +3834,31 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3858,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,12 +3890,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3897,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3945,27 +3953,31 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -3973,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,12 +4009,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4017,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4065,26 +4077,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:40采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4092,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4121,7 +4129,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4131,22 +4139,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4179,29 +4187,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站五莲路归昌路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4211,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,12 +4243,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4250,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4306,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4315,12 +4323,12 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4330,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4354,12 +4362,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4384,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4422,26 +4430,22 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站杨高北路航津路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:10采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4449,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,12 +4477,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4488,17 +4492,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4536,29 +4540,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站云山路灵山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4568,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4592,12 +4596,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4607,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4660,19 +4664,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站云山路灵山路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>10:50采样：该车到重点站五莲路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,7 +4740,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4779,26 +4783,22 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金高路东靖路 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,12 +4830,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4845,22 +4845,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4893,29 +4893,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4964,22 +4964,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5017,24 +5017,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
+          <t>11:10采样：该车到重点站五莲路归昌路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5136,26 +5136,22 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 68分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5163,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,17 +5183,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5207,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5225,24 +5221,24 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5255,30 +5251,34 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5292,47 +5292,872 @@
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 48分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X41" s="2" t="inlineStr">
+      <c r="X44" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="Y44" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>14/18</t>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,22 +3548,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,17 +3905,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,22 +4024,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4778,27 +4778,31 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4806,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,12 +4834,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4855,12 +4859,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4898,24 +4902,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4925,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,12 +4978,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5136,19 +5140,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 68分钟</t>
+          <t>SHMAAS末次终点ETA推算：12:00采样，终点ETA 10分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5183,37 +5187,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5246,29 +5250,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5278,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,12 +5306,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5317,17 +5321,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5365,29 +5369,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 48分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5421,12 +5425,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5436,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5484,29 +5488,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,12 +5544,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5555,22 +5559,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5608,19 +5612,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 37分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,32 +5659,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5723,19 +5727,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 50分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
@@ -5746,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5775,7 +5779,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5800,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5838,24 +5842,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±10分钟</t>
+          <t>12:20采样：该车到重点站杨高北路航津路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5865,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5894,7 +5898,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5914,12 +5918,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5973,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±7分钟</t>
+          <t>12:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5984,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6013,7 +6017,7 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6033,12 +6037,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6152,12 +6156,607 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5493,24 +5493,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5617,14 +5617,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 37分钟</t>
+          <t>SHMAAS末次终点ETA推算：12:40采样，终点ETA 17分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5722,27 +5722,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5750,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,37 +5778,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5837,29 +5841,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站杨高北路航津路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,12 +5897,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5908,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5961,26 +5965,22 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:50采样，终点ETA 45分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6080,24 +6080,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±11分钟</t>
+          <t>12:50采样：该车到重点站金高路万安街 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6199,24 +6199,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+          <t>12:50采样：该车到重点站云山路银山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6318,24 +6318,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+          <t>12:50采样：该车到重点站和龙路草高支路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6751,12 +6751,246 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
           <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -716,18 +716,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +841,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +960,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1069,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1426,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,12 +2852,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,17 +3318,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3915,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4502,12 +4506,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,17 +4972,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5163,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,12 +5335,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5727,12 +5731,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5803,12 +5807,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5850,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5922,12 +5926,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5964,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5977,10 +5981,14 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:50采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5988,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,12 +6020,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6027,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6085,21 +6093,17 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站金高路万安街 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 37分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,12 +6135,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6146,17 +6150,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6199,26 +6203,22 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站云山路银山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,17 +6250,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6270,17 +6270,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6318,24 +6318,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站和龙路草高支路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+          <t>13:10采样：该车到重点站杨高北路（外高桥保税区南站） ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6985,12 +6985,369 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -836,17 +836,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,22 +3552,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,17 +3909,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,14 +4028,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,14 +5444,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5969,24 +5969,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6083,27 +6083,31 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 37分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,12 +6139,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6160,7 +6164,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6198,27 +6202,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6226,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,37 +6258,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6318,26 +6326,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>13:10采样：该车到重点站杨高北路（外高桥保税区南站） ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:00采样，终点ETA 17分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6345,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6374,7 +6378,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6384,17 +6388,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6432,7 +6436,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6449,12 +6453,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6464,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,12 +6492,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6503,14 +6507,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -6518,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6551,29 +6555,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6583,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,12 +6611,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6632,12 +6636,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6670,29 +6674,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,12 +6730,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6751,7 +6755,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6794,19 +6798,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 43分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,17 +6845,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6861,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6909,24 +6913,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+          <t>14:20采样：该车到重点站五莲路凌河路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6960,12 +6964,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6985,12 +6989,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7028,19 +7032,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>14:20采样：该车到重点站杨高北路航津路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7084,7 +7088,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7104,12 +7108,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7152,14 +7156,14 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+          <t>14:20采样：该车到重点站金高路东靖路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7203,7 +7207,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7223,12 +7227,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7266,24 +7270,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+          <t>14:20采样：该车到重点站云山路灵山路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,37 +7321,509 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="X60" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Y60" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>4/18</t>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -831,22 +831,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -950,22 +950,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,22 +2370,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4658,36 +4658,32 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq21推进至seq34，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:50采样：该车到重点站五莲路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4695,18 +4691,30 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>五莲路东陆路</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq17映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4719,37 +4727,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,7 +4871,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4933,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5224,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5338,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,22 +5571,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5758,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,22 +5924,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,7 +6053,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6115,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,12 +6172,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,12 +6291,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6634,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6753,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6793,7 +6801,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6803,17 +6811,21 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 43分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6821,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,12 +6857,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6860,22 +6872,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6908,29 +6920,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站五莲路凌河路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±9分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,12 +6976,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6979,22 +6991,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7027,24 +7039,24 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站杨高北路航津路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -7059,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,12 +7095,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7108,7 +7120,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7163,14 +7175,10 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站金高路东靖路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7178,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7207,7 +7215,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7232,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7265,29 +7273,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站云山路灵山路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7297,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,12 +7329,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7346,12 +7354,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7389,24 +7397,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>15:20采样：该车到重点站五莲路荷泽路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7416,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7445,7 +7453,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7465,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7516,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -7520,14 +7528,10 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 49分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,17 +7563,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7579,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7627,22 +7631,26 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>15:10采样：该车到重点站五莲路凌河路 ETA 29分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7650,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,17 +7682,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7694,17 +7702,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7712,24 +7720,24 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7742,19 +7750,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±5分钟</t>
+          <t>15:20采样：该车到重点站金高路俱进路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7764,12 +7772,12 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7798,32 +7806,1095 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站金高路俱进路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站芳甸路杨高中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>15/18</t>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -836,17 +836,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,22 +1188,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,17 +4028,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5023,36 +5023,32 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq24推进至seq39，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:10采样：该车到重点站五莲路归昌路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5060,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,10 +5064,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5084,37 +5092,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,17 +5222,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5294,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,12 +5341,12 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5348,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,17 +5460,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5532,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,17 +5579,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5647,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,12 +5699,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,17 +6051,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6123,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,17 +6170,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6242,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,17 +6289,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6357,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,12 +6404,12 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6411,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,17 +6523,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,17 +6642,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6714,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,12 +6766,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6833,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,17 +7118,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7158,27 +7166,31 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7186,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,12 +7222,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7225,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7278,12 +7290,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7305,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,17 +7356,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7392,29 +7404,29 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站五莲路荷泽路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7424,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,12 +7460,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7463,17 +7475,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7511,27 +7523,31 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7539,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7563,27 +7579,27 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7593,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7626,29 +7642,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>15:10采样：该车到重点站五莲路凌河路 ETA 29分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±15分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7658,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,12 +7698,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7697,17 +7713,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7745,7 +7761,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7755,19 +7771,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金高路俱进路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7777,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,12 +7817,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7816,22 +7832,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7864,29 +7880,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金高路俱进路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7896,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,12 +7936,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7935,22 +7951,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7988,26 +8004,22 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8015,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8039,12 +8051,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8064,12 +8076,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8107,26 +8119,22 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8134,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8163,7 +8171,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8173,17 +8181,17 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8226,19 +8234,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站芳甸路杨高中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>16:20采样：该车到重点站花山路杨高北路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数11分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -8253,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8302,7 +8310,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8345,19 +8353,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
@@ -8368,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8392,17 +8400,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8412,12 +8420,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8460,7 +8468,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -8472,12 +8480,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+          <t>16:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8487,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8516,7 +8524,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8579,24 +8587,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+          <t>16:20采样：该车到重点站五莲路归昌路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8606,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8635,7 +8643,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8655,12 +8663,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8698,22 +8706,26 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8721,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8745,17 +8757,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8765,17 +8777,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8813,24 +8825,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±11分钟</t>
+          <t>16:20采样：该车到重点站金高路东靖路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8840,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,37 +8876,1223 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站张杨北路金桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站云山路灵山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站花山路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站云山路灵山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>12/18</t>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC81"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,14 +1307,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,17 +2842,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,14 +3080,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,22 +3318,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,17 +4143,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,14 +4742,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,17 +5694,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,17 +5932,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,17 +6761,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,17 +6880,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,22 +7356,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8234,26 +8234,22 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站花山路杨高北路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数11分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:30采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -8261,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8290,7 +8286,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8300,22 +8296,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8344,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -8358,17 +8354,21 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8415,17 +8415,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8534,14 +8534,14 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8582,24 +8582,24 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路归昌路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8653,22 +8653,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8711,19 +8711,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8820,29 +8820,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站金高路东靖路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8939,29 +8939,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站张杨北路金桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9058,29 +9058,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站云山路灵山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9177,29 +9177,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站花山路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9248,22 +9248,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9301,24 +9301,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站云山路灵山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±6分钟</t>
+          <t>17:20采样：该车到重点站大同路石家街（市七医院） ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9420,24 +9420,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+          <t>17:20采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9539,19 +9539,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±6分钟</t>
+          <t>17:20采样：该车到重点站杨高北路夏碧路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9615,12 +9615,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9658,19 +9658,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±8分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -9777,19 +9777,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±7分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±5分钟</t>
+          <t>17:10采样：该车到重点站张杨北路博兴路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10092,7 +10092,1074 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站张杨北路大同路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数101分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数95分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>110分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数110分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,22 +1188,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,22 +5341,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,22 +5460,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,22 +6404,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,22 +7594,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,22 +7713,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,22 +7832,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,22 +7951,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,17 +8186,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8296,22 +8296,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8534,22 +8534,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9063,24 +9063,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9194,12 +9194,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9296,24 +9296,24 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站大同路石家街（市七医院） ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9352,12 +9352,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9415,29 +9415,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9486,22 +9486,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9539,24 +9539,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站杨高北路夏碧路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±6分钟</t>
+          <t>17:40采样：该车到重点站和龙路清溪路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数5分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9615,12 +9615,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9653,29 +9653,29 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9724,22 +9724,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9772,29 +9772,29 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9843,22 +9843,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9891,29 +9891,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:10采样：该车到重点站张杨北路博兴路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9962,22 +9962,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10010,27 +10010,31 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10038,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10062,17 +10066,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10082,17 +10086,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10130,24 +10134,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±9分钟</t>
+          <t>17:50采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10157,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10206,12 +10210,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10249,26 +10253,22 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站张杨北路大同路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10315,22 +10315,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10368,19 +10368,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10487,19 +10487,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车19:25，减去该车自身同类时段历史终点停站中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10553,22 +10553,22 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10606,24 +10606,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±10分钟</t>
+          <t>18:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10725,19 +10725,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数101分钟估算，约±5分钟</t>
+          <t>18:10采样：该车到重点站五莲路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10844,24 +10844,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数95分钟估算，约±9分钟</t>
+          <t>18:20采样：该车到重点站五莲路归昌路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10963,24 +10963,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数110分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站五莲路凌河路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11159,7 +11159,955 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>18:20采样：该车到重点站花山路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>18:20采样：该车到重点站五莲路凌河路 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>90.9</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数95分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>90.8</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8066,22 +8066,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9896,24 +9896,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10015,24 +10015,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10134,26 +10134,22 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:50采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:30采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10161,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10190,7 +10186,7 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10200,22 +10196,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10248,12 +10244,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -10265,10 +10261,14 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10368,19 +10368,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
+          <t>18:30采样：该车到重点站大同路花山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10606,19 +10606,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>18:30采样：该车到重点站杨高北路航津路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10725,24 +10725,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:10采样：该车到重点站五莲路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>18:30采样：该车到重点站金高路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10801,12 +10801,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10844,19 +10844,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站五莲路归昌路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+          <t>18:30采样：该车到重点站金杨路金桥路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10963,24 +10963,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站五莲路凌河路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±10分钟</t>
+          <t>18:30采样：该车到重点站张杨北路博兴路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11197,24 +11197,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站花山路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+          <t>18:30采样：该车到重点站金高路行泰路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11316,19 +11316,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站五莲路凌河路 ETA 34分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>18:30采样：该车到重点站五莲路归昌路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11392,12 +11392,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12111,6 +12111,121 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8653,22 +8653,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9010,22 +9010,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9367,22 +9367,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10015,12 +10015,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10129,27 +10129,31 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:30采样，终点ETA 20分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10157,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10181,12 +10185,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10206,12 +10210,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10276,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10325,12 +10329,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10373,21 +10377,17 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:30采样：该车到重点站大同路花山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:40采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10482,24 +10482,24 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车19:25，减去该车自身同类时段历史终点停站中位数16分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10606,26 +10606,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:30采样：该车到重点站杨高北路航津路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:50采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10633,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10662,7 +10658,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10672,22 +10668,22 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10720,29 +10716,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:30采样：该车到重点站金高路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10752,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10776,12 +10772,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10801,12 +10797,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10839,29 +10835,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>18:30采样：该车到重点站金杨路金桥路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10871,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,12 +10891,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10920,12 +10916,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10958,29 +10954,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>115分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:30采样：该车到重点站张杨北路博兴路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10990,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11014,12 +11010,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11039,12 +11035,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11077,27 +11073,31 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11129,37 +11129,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA90" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11197,26 +11197,22 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>18:30采样：该车到重点站金高路行泰路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11224,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11253,7 +11249,7 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11273,7 +11269,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11316,19 +11312,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>119分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:30采样：该车到重点站五莲路归昌路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站芳甸路杨高中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11343,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11392,12 +11388,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11497,22 +11493,22 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11555,21 +11551,17 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11577,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11601,12 +11593,12 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11626,7 +11618,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11669,24 +11661,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数95分钟估算，约±14分钟</t>
+          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11696,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11720,12 +11712,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11745,12 +11737,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11788,19 +11780,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站金杨路枣庄路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -11815,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11844,7 +11836,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11864,12 +11856,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11907,24 +11899,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±9分钟</t>
+          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11934,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11963,7 +11955,7 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11983,12 +11975,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12102,12 +12094,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12217,12 +12209,369 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>84.4</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC102"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,22 +1188,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,22 +2489,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,22 +7832,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8653,22 +8653,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9015,17 +9015,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9962,22 +9962,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10200,17 +10200,17 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10668,22 +10668,22 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,17 +11149,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11312,19 +11312,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>207分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站芳甸路杨高中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>20:10采样：该车到重点站云山路银山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11426,27 +11426,31 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11454,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11478,17 +11482,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11498,17 +11502,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11541,27 +11545,31 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11569,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11593,12 +11601,12 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11618,12 +11626,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11656,29 +11664,29 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11688,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11712,12 +11720,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11737,12 +11745,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11783,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11792,12 +11800,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金杨路枣庄路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11807,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11831,12 +11839,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11861,7 +11869,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11894,29 +11902,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11926,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11950,12 +11958,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11965,22 +11973,22 @@
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12013,29 +12021,29 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数98分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12045,7 +12053,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12069,12 +12077,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12094,12 +12102,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12132,27 +12140,31 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12160,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12184,32 +12196,32 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12252,26 +12264,22 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12279,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12303,17 +12311,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12323,17 +12331,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12371,24 +12379,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数32分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12398,7 +12406,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12427,7 +12435,7 @@
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12437,22 +12445,22 @@
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12490,24 +12498,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12517,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12546,32 +12554,389 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y102" s="2" t="inlineStr">
+      <c r="Y103" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z102" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA102" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB102" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC102" s="2" t="inlineStr">
-        <is>
-          <t>4/18</t>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东78路.xlsx
+++ b/data/export/2026-09-21-浦东78路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9015,17 +9015,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,17 +11149,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12259,27 +12259,31 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12287,7 +12291,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12311,17 +12315,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12331,17 +12335,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12374,29 +12378,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数32分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12406,7 +12410,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12430,12 +12434,12 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12455,12 +12459,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12493,29 +12497,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12525,7 +12529,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12549,12 +12553,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12574,12 +12578,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12612,29 +12616,29 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12644,7 +12648,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12668,12 +12672,12 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12693,12 +12697,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12736,24 +12740,24 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12763,7 +12767,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12792,7 +12796,7 @@
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12812,7 +12816,7 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
@@ -12882,7 +12886,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12931,12 +12935,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
